--- a/backtest_runs/20260410_193731/by_symbol/ARCTM/ARCTM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/ARCTM/ARCTM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>112450.36</v>
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>121276.84</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>121276.84</v>
@@ -955,7 +955,7 @@
         <v>-8431.800000000005</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>120308.08</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>129565.12</v>
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>138068.68</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>138068.68</v>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>142338.4</v>
@@ -1645,7 +1645,7 @@
         <v>-5310.240000000002</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>137028.16</v>
